--- a/Grupo/UOri_Grupo.xlsx
+++ b/Grupo/UOri_Grupo.xlsx
@@ -458,16 +458,16 @@
         <v>5</v>
       </c>
       <c r="B2" s="2">
-        <v>45.9614108157576</v>
+        <v>45.96141081575762</v>
       </c>
       <c r="C2" s="2">
-        <v>116.1397716057099</v>
+        <v>116.1303572361576</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>6</v>
       </c>
       <c r="E2" s="2">
-        <v>53.37947754818294</v>
+        <v>53.37515057111731</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -475,7 +475,7 @@
         <v>7</v>
       </c>
       <c r="B3" s="2">
-        <v>0.9480657780628304</v>
+        <v>0.9480657780628305</v>
       </c>
       <c r="C3" s="2">
         <v>113.3501047972891</v>
@@ -512,7 +512,7 @@
         <v>15.5234103110175</v>
       </c>
       <c r="C5" s="2">
-        <v>111.138686377915</v>
+        <v>111.1386863779149</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>6</v>
@@ -560,7 +560,7 @@
         <v>12</v>
       </c>
       <c r="B8" s="2">
-        <v>5.399730717074967</v>
+        <v>5.399730717074966</v>
       </c>
       <c r="C8" s="2">
         <v>106.0215922642991</v>
@@ -569,7 +569,7 @@
         <v>6</v>
       </c>
       <c r="E8" s="2">
-        <v>5.724880484227339</v>
+        <v>5.724880484227338</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -586,7 +586,7 @@
         <v>6</v>
       </c>
       <c r="E9" s="2">
-        <v>0.6054670492205254</v>
+        <v>0.6054670492205255</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -594,7 +594,7 @@
         <v>14</v>
       </c>
       <c r="B10" s="2">
-        <v>0.4555798201050708</v>
+        <v>0.4555798201050709</v>
       </c>
       <c r="C10" s="2">
         <v>111.9525560063853</v>
@@ -611,7 +611,7 @@
         <v>15</v>
       </c>
       <c r="B11" s="2">
-        <v>4.264527890686297</v>
+        <v>4.264527890686298</v>
       </c>
       <c r="C11" s="2">
         <v>129.8761678125319</v>
@@ -620,7 +620,7 @@
         <v>6</v>
       </c>
       <c r="E11" s="2">
-        <v>5.538605399719963</v>
+        <v>5.538605399719964</v>
       </c>
     </row>
     <row r="12" spans="1:5">
